--- a/MinMax/scripts/comparison/violations_comparison_table_118_1000.xlsx
+++ b/MinMax/scripts/comparison/violations_comparison_table_118_1000.xlsx
@@ -459,16 +459,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.000899133738130331</v>
+        <v>0.0009432394872419536</v>
       </c>
       <c r="C2">
-        <v>0.000630323716904968</v>
+        <v>0.0006547512020915747</v>
       </c>
       <c r="D2">
-        <v>0.01155088562518358</v>
+        <v>0.01169854588806629</v>
       </c>
       <c r="E2">
-        <v>0.01444919127970934</v>
+        <v>0.01449902914464474</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -476,16 +476,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.2491235136985779</v>
+        <v>0.2417278289794922</v>
       </c>
       <c r="C3">
-        <v>0.2743224501609802</v>
+        <v>0.2614558935165405</v>
       </c>
       <c r="D3">
-        <v>0.2947475910186768</v>
+        <v>0.300350546836853</v>
       </c>
       <c r="E3">
-        <v>0.5326957702636719</v>
+        <v>0.5340533256530762</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -493,16 +493,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.0003060545714106411</v>
+        <v>0.0002890683244913816</v>
       </c>
       <c r="C4">
-        <v>0.0003195730387233198</v>
+        <v>0.0002865739807020873</v>
       </c>
       <c r="D4">
-        <v>0.007606826722621918</v>
+        <v>0.007448134012520313</v>
       </c>
       <c r="E4">
-        <v>0.006614109966903925</v>
+        <v>0.006395391654223204</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -510,16 +510,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.0801096186041832</v>
+        <v>0.06732925027608871</v>
       </c>
       <c r="C5">
-        <v>0.1765499114990234</v>
+        <v>0.1722598224878311</v>
       </c>
       <c r="D5">
-        <v>0.233913779258728</v>
+        <v>0.2489813566207886</v>
       </c>
       <c r="E5">
-        <v>0.246779203414917</v>
+        <v>0.2816541194915771</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -533,10 +533,10 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.0002011964534176514</v>
+        <v>0.0002229774690931663</v>
       </c>
       <c r="E6">
-        <v>0.001691584358923137</v>
+        <v>0.001664481358602643</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -550,10 +550,10 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0.1128673851490021</v>
+        <v>0.08243787288665771</v>
       </c>
       <c r="E7">
-        <v>0.08567176759243011</v>
+        <v>0.08644096553325653</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -567,10 +567,10 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.0005288341781124473</v>
+        <v>0.0005207809736020863</v>
       </c>
       <c r="E8">
-        <v>0.002483172342181206</v>
+        <v>0.0024838971439749</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -584,10 +584,10 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.08238571882247925</v>
+        <v>0.07313460111618042</v>
       </c>
       <c r="E9">
-        <v>0.1126970648765564</v>
+        <v>0.08994597196578979</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -601,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1.759946462698281E-05</v>
+        <v>1.57050890265964E-05</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.02162134647369385</v>
+        <v>0.01949214935302734</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -629,10 +629,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.0001610882172826678</v>
+        <v>0.0001610425824765116</v>
       </c>
       <c r="C12">
-        <v>0.0001610887557035312</v>
+        <v>0.0001610440376680344</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -646,10 +646,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.01924526691436768</v>
+        <v>0.01923900842666626</v>
       </c>
       <c r="C13">
-        <v>0.01925069093704224</v>
+        <v>0.0192447304725647</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -663,10 +663,10 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.1711653172969818</v>
+        <v>0.171148806810379</v>
       </c>
       <c r="C14">
-        <v>0.1711658239364624</v>
+        <v>0.1711494475603104</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>8.237672805786133</v>
+        <v>8.236589431762695</v>
       </c>
       <c r="C15">
-        <v>8.239147186279297</v>
+        <v>8.238193511962891</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -697,16 +697,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>6.203114424975072E-08</v>
+        <v>6.211028524989059E-08</v>
       </c>
       <c r="C16">
-        <v>6.207356358214393E-08</v>
+        <v>6.168666077159549E-08</v>
       </c>
       <c r="D16">
-        <v>1.948487090140973E-06</v>
+        <v>1.947109058659274E-06</v>
       </c>
       <c r="E16">
-        <v>1.93048500321531E-06</v>
+        <v>1.929447361476091E-06</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -714,16 +714,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>3.932305043674366E-06</v>
+        <v>4.316786444862859E-06</v>
       </c>
       <c r="C17">
-        <v>4.105989514898887E-06</v>
+        <v>3.920034779439785E-06</v>
       </c>
       <c r="D17">
-        <v>5.091357535442442E-05</v>
+        <v>4.729237403741144E-05</v>
       </c>
       <c r="E17">
-        <v>5.644288127788742E-05</v>
+        <v>5.45475630362184E-05</v>
       </c>
     </row>
   </sheetData>

--- a/MinMax/scripts/comparison/violations_comparison_table_118_1000.xlsx
+++ b/MinMax/scripts/comparison/violations_comparison_table_118_1000.xlsx
@@ -459,16 +459,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.0009432394872419536</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0006547512020915747</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0.01169854588806629</v>
+        <v>0.01169854868203402</v>
       </c>
       <c r="E2">
-        <v>0.01449902914464474</v>
+        <v>0.01449902728199959</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -476,16 +476,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.2417278289794922</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.2614558935165405</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0.300350546836853</v>
       </c>
       <c r="E3">
-        <v>0.5340533256530762</v>
+        <v>0.5340538024902344</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -493,16 +493,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.0002890683244913816</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.0002865739807020873</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0.007448134012520313</v>
+        <v>0.007448130287230015</v>
       </c>
       <c r="E4">
-        <v>0.006395391654223204</v>
+        <v>0.00639539398252964</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -510,13 +510,13 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.06732925027608871</v>
+        <v>-0</v>
       </c>
       <c r="C5">
-        <v>0.1722598224878311</v>
+        <v>-0</v>
       </c>
       <c r="D5">
-        <v>0.2489813566207886</v>
+        <v>0.2489832639694214</v>
       </c>
       <c r="E5">
         <v>0.2816541194915771</v>
@@ -533,10 +533,10 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.0002229774690931663</v>
+        <v>0.0002229776582680643</v>
       </c>
       <c r="E6">
-        <v>0.001664481358602643</v>
+        <v>0.001664479146711528</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -550,7 +550,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0.08243787288665771</v>
+        <v>0.08243805170059204</v>
       </c>
       <c r="E7">
         <v>0.08644096553325653</v>
@@ -567,10 +567,10 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.0005207809736020863</v>
+        <v>0.0005207826616242528</v>
       </c>
       <c r="E8">
-        <v>0.0024838971439749</v>
+        <v>0.002483891788870096</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -584,10 +584,10 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.07313460111618042</v>
+        <v>0.0731348991394043</v>
       </c>
       <c r="E9">
-        <v>0.08994597196578979</v>
+        <v>0.08994612097740173</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -601,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1.57050890265964E-05</v>
+        <v>1.570508175063878E-05</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -629,10 +629,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.0001610425824765116</v>
+        <v>0.0001610597391845658</v>
       </c>
       <c r="C12">
-        <v>0.0001610440376680344</v>
+        <v>0.0001610548788448796</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -646,10 +646,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.01923900842666626</v>
+        <v>0.01923835277557373</v>
       </c>
       <c r="C13">
-        <v>0.0192447304725647</v>
+        <v>0.01924300193786621</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -663,10 +663,10 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.171148806810379</v>
+        <v>0.1711557507514954</v>
       </c>
       <c r="C14">
-        <v>0.1711494475603104</v>
+        <v>0.1711530387401581</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>8.236589431762695</v>
+        <v>8.236259460449219</v>
       </c>
       <c r="C15">
-        <v>8.238193511962891</v>
+        <v>8.236791610717773</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -697,16 +697,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>6.211028524989059E-08</v>
+        <v>6.316329895216988E-08</v>
       </c>
       <c r="C16">
-        <v>6.168666077159549E-08</v>
+        <v>6.32341516540486E-08</v>
       </c>
       <c r="D16">
-        <v>1.947109058659274E-06</v>
+        <v>1.938622972375015E-06</v>
       </c>
       <c r="E16">
-        <v>1.929447361476091E-06</v>
+        <v>1.921265493365354E-06</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -714,16 +714,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>4.316786444862859E-06</v>
+        <v>4.464574540400787E-06</v>
       </c>
       <c r="C17">
-        <v>3.920034779439785E-06</v>
+        <v>4.363228405310887E-06</v>
       </c>
       <c r="D17">
-        <v>4.729237403741144E-05</v>
+        <v>4.912617805530317E-05</v>
       </c>
       <c r="E17">
-        <v>5.45475630362184E-05</v>
+        <v>5.442745532491244E-05</v>
       </c>
     </row>
   </sheetData>
